--- a/InputData/endo-learn/BGSaWC/BAU Global Solar and Wind Cap.xlsx
+++ b/InputData/endo-learn/BGSaWC/BAU Global Solar and Wind Cap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\endo-learn\BGSaWC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A3E957-53A7-4AA8-ACE3-415FAF5084C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8AB34D6-DACA-4B22-AB58-AFB8ABFF4382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -181,7 +181,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -289,7 +289,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -573,17 +573,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -591,72 +591,72 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="2">
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B10" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>2024</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -669,12 +669,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AG7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B1">
         <v>2021</v>
       </c>
@@ -685,7 +685,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -699,7 +699,7 @@
         <v>12639</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -713,7 +713,7 @@
         <v>3874</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>2019</v>
       </c>
@@ -811,7 +811,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -944,7 +944,7 @@
         <v>12638999.999999885</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1085,12 +1085,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9031182-2635-4560-BFB8-5BE251E4AFFA}">
   <dimension ref="A1:AF4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="9"/>
       <c r="B1" s="10">
         <v>2020</v>
@@ -1186,7 +1186,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>4167.711163284006</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>548.97100501700004</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1522,20 +1522,20 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AF25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="25.453125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B1">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
@@ -1559,7 +1559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1575,13 +1575,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="5">
-        <f>'Global Renewables Outlook'!C7*(1-Wind!B4)</f>
-        <v>656129.54939927824</v>
+        <f>'Global Renewables Outlook'!F7*(1-Wind!E4)</f>
+        <v>1022725.7338070514</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1614,13 +1614,13 @@
       <c r="AE7" s="5"/>
       <c r="AF7" s="5"/>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="5">
-        <f>'Global Renewables Outlook'!C6</f>
-        <v>505426.66666663717</v>
+        <f>'Global Renewables Outlook'!E6</f>
+        <v>1344133.3333333023</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1653,7 +1653,7 @@
       <c r="AE8" s="5"/>
       <c r="AF8" s="5"/>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
@@ -1701,13 +1701,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="5">
-        <f>'Global Renewables Outlook'!C7*Wind!B4</f>
-        <v>33426.00615628378</v>
+        <f>'Global Renewables Outlook'!F7*Wind!E4</f>
+        <v>79163.155081824472</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -1740,7 +1740,7 @@
       <c r="AE15" s="5"/>
       <c r="AF15" s="5"/>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>35</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>36</v>
       </c>
@@ -1830,108 +1830,99 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AB25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="25.453125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B1">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="C1">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D1">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="E1">
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="F1">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="G1">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="H1">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="I1">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="J1">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="K1">
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="L1">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="M1">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="N1">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="O1">
-        <v>2034</v>
+        <v>2037</v>
       </c>
       <c r="P1">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="Q1">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="R1">
-        <v>2037</v>
+        <v>2040</v>
       </c>
       <c r="S1">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="T1">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="U1">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="V1">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="W1">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="X1">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="Y1">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="Z1">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="AA1">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="AB1">
-        <v>2047</v>
-      </c>
-      <c r="AC1">
-        <v>2048</v>
-      </c>
-      <c r="AD1">
-        <v>2049</v>
-      </c>
-      <c r="AE1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -2016,17 +2007,8 @@
       <c r="AB2">
         <v>0</v>
       </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
@@ -2111,17 +2093,8 @@
       <c r="AB3">
         <v>0</v>
       </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
@@ -2206,17 +2179,8 @@
       <c r="AB4">
         <v>0</v>
       </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -2301,17 +2265,8 @@
       <c r="AB5">
         <v>0</v>
       </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -2396,267 +2351,234 @@
       <c r="AB6">
         <v>0</v>
       </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="5">
-        <f>'Global Renewables Outlook'!D7*(1-Wind!C4)</f>
-        <v>775076.77210135513</v>
-      </c>
-      <c r="C7" s="5">
-        <f>'Global Renewables Outlook'!E7*(1-Wind!D4)</f>
-        <v>900121.1891292074</v>
-      </c>
-      <c r="D7" s="5">
-        <f>'Global Renewables Outlook'!F7*(1-Wind!E4)</f>
-        <v>1022725.7338070514</v>
-      </c>
-      <c r="E7" s="5">
         <f>'Global Renewables Outlook'!G7*(1-Wind!F4)</f>
         <v>1136893.5130293544</v>
       </c>
-      <c r="F7" s="5">
+      <c r="C7" s="5">
         <f>'Global Renewables Outlook'!H7*(1-Wind!G4)</f>
         <v>1250773.9377340297</v>
       </c>
-      <c r="G7" s="5">
+      <c r="D7" s="5">
         <f>'Global Renewables Outlook'!I7*(1-Wind!H4)</f>
         <v>1362489.7806542467</v>
       </c>
-      <c r="H7" s="5">
+      <c r="E7" s="5">
         <f>'Global Renewables Outlook'!J7*(1-Wind!I4)</f>
         <v>1478640.9639649629</v>
       </c>
-      <c r="I7" s="5">
+      <c r="F7" s="5">
         <f>'Global Renewables Outlook'!K7*(1-Wind!J4)</f>
         <v>1597697.3311929598</v>
       </c>
-      <c r="J7" s="5">
+      <c r="G7" s="5">
         <f>'Global Renewables Outlook'!L7*(1-Wind!K4)</f>
         <v>1711604.7180015468</v>
       </c>
-      <c r="K7" s="5">
+      <c r="H7" s="5">
         <f>'Global Renewables Outlook'!M7*(1-Wind!L4)</f>
         <v>1819392.3548773606</v>
       </c>
-      <c r="L7" s="5">
+      <c r="I7" s="5">
         <f>'Global Renewables Outlook'!N7*(1-Wind!M4)</f>
         <v>1875002.5415982381</v>
       </c>
-      <c r="M7" s="5">
+      <c r="J7" s="5">
         <f>'Global Renewables Outlook'!O7*(1-Wind!N4)</f>
         <v>1927756.7115537715</v>
       </c>
-      <c r="N7" s="5">
+      <c r="K7" s="5">
         <f>'Global Renewables Outlook'!P7*(1-Wind!O4)</f>
         <v>1987962.964126393</v>
       </c>
-      <c r="O7" s="5">
+      <c r="L7" s="5">
         <f>'Global Renewables Outlook'!Q7*(1-Wind!P4)</f>
         <v>2048972.6988752473</v>
       </c>
-      <c r="P7" s="5">
+      <c r="M7" s="5">
         <f>'Global Renewables Outlook'!R7*(1-Wind!Q4)</f>
         <v>2129959.9682737119</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="N7" s="5">
         <f>'Global Renewables Outlook'!S7*(1-Wind!R4)</f>
         <v>2215932.3022829583</v>
       </c>
-      <c r="R7" s="5">
+      <c r="O7" s="5">
         <f>'Global Renewables Outlook'!T7*(1-Wind!S4)</f>
         <v>2299960.4441534309</v>
       </c>
-      <c r="S7" s="5">
+      <c r="P7" s="5">
         <f>'Global Renewables Outlook'!U7*(1-Wind!T4)</f>
         <v>2383142.2667729277</v>
       </c>
-      <c r="T7" s="5">
+      <c r="Q7" s="5">
         <f>'Global Renewables Outlook'!V7*(1-Wind!U4)</f>
         <v>2468216.8235020074</v>
       </c>
-      <c r="U7" s="5">
+      <c r="R7" s="5">
         <f>'Global Renewables Outlook'!W7*(1-Wind!V4)</f>
         <v>2550880.1051850733</v>
       </c>
-      <c r="V7" s="5">
+      <c r="S7" s="5">
         <f>'Global Renewables Outlook'!X7*(1-Wind!W4)</f>
         <v>2634875.7242717026</v>
       </c>
-      <c r="W7" s="5">
+      <c r="T7" s="5">
         <f>'Global Renewables Outlook'!Y7*(1-Wind!X4)</f>
         <v>2719858.0306125535</v>
       </c>
-      <c r="X7" s="5">
+      <c r="U7" s="5">
         <f>'Global Renewables Outlook'!Z7*(1-Wind!Y4)</f>
         <v>2805844.6273935628</v>
       </c>
-      <c r="Y7" s="5">
+      <c r="V7" s="5">
         <f>'Global Renewables Outlook'!AA7*(1-Wind!Z4)</f>
         <v>2890101.1357675246</v>
       </c>
-      <c r="Z7" s="5">
+      <c r="W7" s="5">
         <f>'Global Renewables Outlook'!AB7*(1-Wind!AA4)</f>
         <v>2972372.4111485863</v>
       </c>
-      <c r="AA7" s="5">
+      <c r="X7" s="5">
         <f>'Global Renewables Outlook'!AC7*(1-Wind!AB4)</f>
         <v>3062242.8847385035</v>
       </c>
-      <c r="AB7" s="5">
+      <c r="Y7" s="5">
         <f>'Global Renewables Outlook'!AD7*(1-Wind!AC4)</f>
         <v>3154247.9605017747</v>
       </c>
-      <c r="AC7" s="5">
+      <c r="Z7" s="5">
         <f>'Global Renewables Outlook'!AE7*(1-Wind!AD4)</f>
         <v>3241643.3280328619</v>
       </c>
-      <c r="AD7" s="5">
+      <c r="AA7" s="5">
         <f>'Global Renewables Outlook'!AF7*(1-Wind!AE4)</f>
         <v>3329824.154709897</v>
       </c>
-      <c r="AE7" s="5">
+      <c r="AB7" s="5">
         <f>'Global Renewables Outlook'!AG7*(1-Wind!AF4)</f>
         <v>3423108.1235600994</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="5">
-        <f>'Global Renewables Outlook'!D6</f>
-        <v>924779.99999991152</v>
-      </c>
-      <c r="C8" s="5">
-        <f>'Global Renewables Outlook'!E6</f>
-        <v>1344133.3333333023</v>
-      </c>
-      <c r="D8" s="5">
-        <f>'Global Renewables Outlook'!F6</f>
-        <v>1763486.6666665766</v>
-      </c>
-      <c r="E8" s="5">
         <f>'Global Renewables Outlook'!G6</f>
         <v>2182839.9999999674</v>
       </c>
-      <c r="F8" s="5">
+      <c r="C8" s="5">
         <f>'Global Renewables Outlook'!H6</f>
         <v>2602193.3333332418</v>
       </c>
-      <c r="G8" s="5">
+      <c r="D8" s="5">
         <f>'Global Renewables Outlook'!I6</f>
         <v>3021546.6666666325</v>
       </c>
-      <c r="H8" s="5">
+      <c r="E8" s="5">
         <f>'Global Renewables Outlook'!J6</f>
         <v>3440899.9999999069</v>
       </c>
-      <c r="I8" s="5">
+      <c r="F8" s="5">
         <f>'Global Renewables Outlook'!K6</f>
         <v>3860253.3333332976</v>
       </c>
-      <c r="J8" s="5">
+      <c r="G8" s="5">
         <f>'Global Renewables Outlook'!L6</f>
         <v>4279606.666666572</v>
       </c>
-      <c r="K8" s="5">
+      <c r="H8" s="5">
         <f>'Global Renewables Outlook'!M6</f>
         <v>4698959.9999999627</v>
       </c>
-      <c r="L8" s="5">
+      <c r="I8" s="5">
         <f>'Global Renewables Outlook'!N6</f>
         <v>5095961.9999999413</v>
       </c>
-      <c r="M8" s="5">
+      <c r="J8" s="5">
         <f>'Global Renewables Outlook'!O6</f>
         <v>5492963.9999999199</v>
       </c>
-      <c r="N8" s="5">
+      <c r="K8" s="5">
         <f>'Global Renewables Outlook'!P6</f>
         <v>5889965.9999998985</v>
       </c>
-      <c r="O8" s="5">
+      <c r="L8" s="5">
         <f>'Global Renewables Outlook'!Q6</f>
         <v>6286967.9999998771</v>
       </c>
-      <c r="P8" s="5">
+      <c r="M8" s="5">
         <f>'Global Renewables Outlook'!R6</f>
         <v>6683969.9999999721</v>
       </c>
-      <c r="Q8" s="5">
+      <c r="N8" s="5">
         <f>'Global Renewables Outlook'!S6</f>
         <v>7080971.9999999506</v>
       </c>
-      <c r="R8" s="5">
+      <c r="O8" s="5">
         <f>'Global Renewables Outlook'!T6</f>
         <v>7477973.9999999292</v>
       </c>
-      <c r="S8" s="5">
+      <c r="P8" s="5">
         <f>'Global Renewables Outlook'!U6</f>
         <v>7874975.9999999078</v>
       </c>
-      <c r="T8" s="5">
+      <c r="Q8" s="5">
         <f>'Global Renewables Outlook'!V6</f>
         <v>8271977.9999998864</v>
       </c>
-      <c r="U8" s="5">
+      <c r="R8" s="5">
         <f>'Global Renewables Outlook'!W6</f>
         <v>8668979.9999999814</v>
       </c>
-      <c r="V8" s="5">
+      <c r="S8" s="5">
         <f>'Global Renewables Outlook'!X6</f>
         <v>9065981.999999959</v>
       </c>
-      <c r="W8" s="5">
+      <c r="T8" s="5">
         <f>'Global Renewables Outlook'!Y6</f>
         <v>9462983.9999999385</v>
       </c>
-      <c r="X8" s="5">
+      <c r="U8" s="5">
         <f>'Global Renewables Outlook'!Z6</f>
         <v>9859985.999999918</v>
       </c>
-      <c r="Y8" s="5">
+      <c r="V8" s="5">
         <f>'Global Renewables Outlook'!AA6</f>
         <v>10256987.999999896</v>
       </c>
-      <c r="Z8" s="5">
+      <c r="W8" s="5">
         <f>'Global Renewables Outlook'!AB6</f>
         <v>10653989.999999873</v>
       </c>
-      <c r="AA8" s="5">
+      <c r="X8" s="5">
         <f>'Global Renewables Outlook'!AC6</f>
         <v>11050991.99999997</v>
       </c>
-      <c r="AB8" s="5">
+      <c r="Y8" s="5">
         <f>'Global Renewables Outlook'!AD6</f>
         <v>11447993.999999948</v>
       </c>
-      <c r="AC8" s="5">
+      <c r="Z8" s="5">
         <f>'Global Renewables Outlook'!AE6</f>
         <v>11844995.999999925</v>
       </c>
-      <c r="AD8" s="5">
+      <c r="AA8" s="5">
         <f>'Global Renewables Outlook'!AF6</f>
         <v>12241997.999999905</v>
       </c>
-      <c r="AE8" s="5">
+      <c r="AB8" s="5">
         <f>'Global Renewables Outlook'!AG6</f>
         <v>12638999.999999885</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2741,17 +2663,8 @@
       <c r="AB9">
         <v>0</v>
       </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -2836,17 +2749,8 @@
       <c r="AB10">
         <v>0</v>
       </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -2931,17 +2835,8 @@
       <c r="AB11">
         <v>0</v>
       </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
@@ -3026,17 +2921,8 @@
       <c r="AB12">
         <v>0</v>
       </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
@@ -3121,17 +3007,8 @@
       <c r="AB13">
         <v>0</v>
       </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
@@ -3216,142 +3093,121 @@
       <c r="AB14">
         <v>0</v>
       </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="5">
-        <f>'Global Renewables Outlook'!D7*Wind!B4</f>
-        <v>40088.585855819823</v>
-      </c>
-      <c r="C15" s="5">
-        <f>'Global Renewables Outlook'!E7*Wind!C4</f>
-        <v>60552.682810726183</v>
-      </c>
-      <c r="D15" s="5">
-        <f>'Global Renewables Outlook'!F7*Wind!D4</f>
-        <v>73490.060248979091</v>
-      </c>
-      <c r="E15" s="5">
         <f>'Global Renewables Outlook'!G7*Wind!E4</f>
         <v>89037.595218580886</v>
       </c>
-      <c r="F15" s="5">
+      <c r="C15" s="5">
         <f>'Global Renewables Outlook'!H7*Wind!F4</f>
         <v>113800.59291611612</v>
       </c>
-      <c r="G15" s="5">
+      <c r="D15" s="5">
         <f>'Global Renewables Outlook'!I7*Wind!G4</f>
         <v>138582.86918859708</v>
       </c>
-      <c r="H15" s="5">
+      <c r="E15" s="5">
         <f>'Global Renewables Outlook'!J7*Wind!H4</f>
         <v>165505.04431378981</v>
       </c>
-      <c r="I15" s="5">
+      <c r="F15" s="5">
         <f>'Global Renewables Outlook'!K7*Wind!I4</f>
         <v>187424.14160128735</v>
       </c>
-      <c r="J15" s="5">
+      <c r="G15" s="5">
         <f>'Global Renewables Outlook'!L7*Wind!J4</f>
         <v>206118.71382443423</v>
       </c>
-      <c r="K15" s="5">
+      <c r="H15" s="5">
         <f>'Global Renewables Outlook'!M7*Wind!K4</f>
         <v>230285.87337236118</v>
       </c>
-      <c r="L15" s="5">
+      <c r="I15" s="5">
         <f>'Global Renewables Outlook'!N7*Wind!L4</f>
         <v>255332.93188794897</v>
       </c>
-      <c r="M15" s="5">
+      <c r="J15" s="5">
         <f>'Global Renewables Outlook'!O7*Wind!M4</f>
         <v>291237.77865488769</v>
       </c>
-      <c r="N15" s="5">
+      <c r="K15" s="5">
         <f>'Global Renewables Outlook'!P7*Wind!N4</f>
         <v>330031.93771321455</v>
       </c>
-      <c r="O15" s="5">
+      <c r="L15" s="5">
         <f>'Global Renewables Outlook'!Q7*Wind!O4</f>
         <v>361004.00300979265</v>
       </c>
-      <c r="P15" s="5">
+      <c r="M15" s="5">
         <f>'Global Renewables Outlook'!R7*Wind!P4</f>
         <v>391092.00464981049</v>
       </c>
-      <c r="Q15" s="5">
+      <c r="N15" s="5">
         <f>'Global Renewables Outlook'!S7*Wind!Q4</f>
         <v>400441.03425807011</v>
       </c>
-      <c r="R15" s="5">
+      <c r="O15" s="5">
         <f>'Global Renewables Outlook'!T7*Wind!R4</f>
         <v>404643.31207967794</v>
       </c>
-      <c r="S15" s="5">
+      <c r="P15" s="5">
         <f>'Global Renewables Outlook'!U7*Wind!S4</f>
         <v>410876.84215022629</v>
       </c>
-      <c r="T15" s="5">
+      <c r="Q15" s="5">
         <f>'Global Renewables Outlook'!V7*Wind!T4</f>
         <v>417999.63597350329</v>
       </c>
-      <c r="U15" s="5">
+      <c r="R15" s="5">
         <f>'Global Renewables Outlook'!W7*Wind!U4</f>
         <v>423182.47386574256</v>
       </c>
-      <c r="V15" s="5">
+      <c r="S15" s="5">
         <f>'Global Renewables Outlook'!X7*Wind!V4</f>
         <v>430864.87645209447</v>
       </c>
-      <c r="W15" s="5">
+      <c r="T15" s="5">
         <f>'Global Renewables Outlook'!Y7*Wind!W4</f>
         <v>437184.66041645262</v>
       </c>
-      <c r="X15" s="5">
+      <c r="U15" s="5">
         <f>'Global Renewables Outlook'!Z7*Wind!X4</f>
         <v>442500.01644445065</v>
       </c>
-      <c r="Y15" s="5">
+      <c r="V15" s="5">
         <f>'Global Renewables Outlook'!AA7*Wind!Y4</f>
         <v>446794.33610616927</v>
       </c>
-      <c r="Z15" s="5">
+      <c r="W15" s="5">
         <f>'Global Renewables Outlook'!AB7*Wind!Z4</f>
         <v>452877.65354890848</v>
       </c>
-      <c r="AA15" s="5">
+      <c r="X15" s="5">
         <f>'Global Renewables Outlook'!AC7*Wind!AA4</f>
         <v>461007.18750435935</v>
       </c>
-      <c r="AB15" s="5">
+      <c r="Y15" s="5">
         <f>'Global Renewables Outlook'!AD7*Wind!AB4</f>
         <v>461346.81313483516</v>
       </c>
-      <c r="AC15" s="5">
+      <c r="Z15" s="5">
         <f>'Global Renewables Outlook'!AE7*Wind!AC4</f>
         <v>459512.7777562656</v>
       </c>
-      <c r="AD15" s="5">
+      <c r="AA15" s="5">
         <f>'Global Renewables Outlook'!AF7*Wind!AD4</f>
         <v>462417.53814992314</v>
       </c>
-      <c r="AE15" s="5">
+      <c r="AB15" s="5">
         <f>'Global Renewables Outlook'!AG7*Wind!AE4</f>
         <v>464527.61322951212</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
@@ -3436,17 +3292,8 @@
       <c r="AB16">
         <v>0</v>
       </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -3531,17 +3378,8 @@
       <c r="AB17">
         <v>0</v>
       </c>
-      <c r="AC17">
-        <v>0</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
@@ -3626,17 +3464,8 @@
       <c r="AB18">
         <v>0</v>
       </c>
-      <c r="AC18">
-        <v>0</v>
-      </c>
-      <c r="AD18">
-        <v>0</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -3721,17 +3550,8 @@
       <c r="AB19">
         <v>0</v>
       </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -3816,17 +3636,8 @@
       <c r="AB20">
         <v>0</v>
       </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -3911,17 +3722,8 @@
       <c r="AB21">
         <v>0</v>
       </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -4006,17 +3808,8 @@
       <c r="AB22">
         <v>0</v>
       </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -4101,17 +3894,8 @@
       <c r="AB23">
         <v>0</v>
       </c>
-      <c r="AC23">
-        <v>0</v>
-      </c>
-      <c r="AD23">
-        <v>0</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>35</v>
       </c>
@@ -4196,17 +3980,8 @@
       <c r="AB24">
         <v>0</v>
       </c>
-      <c r="AC24">
-        <v>0</v>
-      </c>
-      <c r="AD24">
-        <v>0</v>
-      </c>
-      <c r="AE24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>36</v>
       </c>
@@ -4289,15 +4064,6 @@
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0</v>
-      </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
-      <c r="AE25">
         <v>0</v>
       </c>
     </row>

--- a/InputData/endo-learn/BGSaWC/BAU Global Solar and Wind Cap.xlsx
+++ b/InputData/endo-learn/BGSaWC/BAU Global Solar and Wind Cap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\endo-learn\BGSaWC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8AB34D6-DACA-4B22-AB58-AFB8ABFF4382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A3E957-53A7-4AA8-ACE3-415FAF5084C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -181,7 +181,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -289,7 +289,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -573,17 +573,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -591,72 +591,72 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
         <v>2024</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -669,12 +669,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AG7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B1">
         <v>2021</v>
       </c>
@@ -685,7 +685,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -699,7 +699,7 @@
         <v>12639</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -713,7 +713,7 @@
         <v>3874</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>2019</v>
       </c>
@@ -811,7 +811,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -944,7 +944,7 @@
         <v>12638999.999999885</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1085,12 +1085,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9031182-2635-4560-BFB8-5BE251E4AFFA}">
   <dimension ref="A1:AF4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="9"/>
       <c r="B1" s="10">
         <v>2020</v>
@@ -1186,7 +1186,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>4167.711163284006</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>548.97100501700004</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1522,20 +1522,20 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AF25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.453125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B1">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
@@ -1559,7 +1559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1575,13 +1575,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="5">
-        <f>'Global Renewables Outlook'!F7*(1-Wind!E4)</f>
-        <v>1022725.7338070514</v>
+        <f>'Global Renewables Outlook'!C7*(1-Wind!B4)</f>
+        <v>656129.54939927824</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1614,13 +1614,13 @@
       <c r="AE7" s="5"/>
       <c r="AF7" s="5"/>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="5">
-        <f>'Global Renewables Outlook'!E6</f>
-        <v>1344133.3333333023</v>
+        <f>'Global Renewables Outlook'!C6</f>
+        <v>505426.66666663717</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1653,7 +1653,7 @@
       <c r="AE8" s="5"/>
       <c r="AF8" s="5"/>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
@@ -1701,13 +1701,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="5">
-        <f>'Global Renewables Outlook'!F7*Wind!E4</f>
-        <v>79163.155081824472</v>
+        <f>'Global Renewables Outlook'!C7*Wind!B4</f>
+        <v>33426.00615628378</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -1740,7 +1740,7 @@
       <c r="AE15" s="5"/>
       <c r="AF15" s="5"/>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>35</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>36</v>
       </c>
@@ -1830,99 +1830,108 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AB25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AE25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.453125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B1">
+        <v>2021</v>
+      </c>
+      <c r="C1">
+        <v>2022</v>
+      </c>
+      <c r="D1">
+        <v>2023</v>
+      </c>
+      <c r="E1">
         <v>2024</v>
       </c>
-      <c r="C1">
+      <c r="F1">
         <v>2025</v>
       </c>
-      <c r="D1">
+      <c r="G1">
         <v>2026</v>
       </c>
-      <c r="E1">
+      <c r="H1">
         <v>2027</v>
       </c>
-      <c r="F1">
+      <c r="I1">
         <v>2028</v>
       </c>
-      <c r="G1">
+      <c r="J1">
         <v>2029</v>
       </c>
-      <c r="H1">
+      <c r="K1">
         <v>2030</v>
       </c>
-      <c r="I1">
+      <c r="L1">
         <v>2031</v>
       </c>
-      <c r="J1">
+      <c r="M1">
         <v>2032</v>
       </c>
-      <c r="K1">
+      <c r="N1">
         <v>2033</v>
       </c>
-      <c r="L1">
+      <c r="O1">
         <v>2034</v>
       </c>
-      <c r="M1">
+      <c r="P1">
         <v>2035</v>
       </c>
-      <c r="N1">
+      <c r="Q1">
         <v>2036</v>
       </c>
-      <c r="O1">
+      <c r="R1">
         <v>2037</v>
       </c>
-      <c r="P1">
+      <c r="S1">
         <v>2038</v>
       </c>
-      <c r="Q1">
+      <c r="T1">
         <v>2039</v>
       </c>
-      <c r="R1">
+      <c r="U1">
         <v>2040</v>
       </c>
-      <c r="S1">
+      <c r="V1">
         <v>2041</v>
       </c>
-      <c r="T1">
+      <c r="W1">
         <v>2042</v>
       </c>
-      <c r="U1">
+      <c r="X1">
         <v>2043</v>
       </c>
-      <c r="V1">
+      <c r="Y1">
         <v>2044</v>
       </c>
-      <c r="W1">
+      <c r="Z1">
         <v>2045</v>
       </c>
-      <c r="X1">
+      <c r="AA1">
         <v>2046</v>
       </c>
-      <c r="Y1">
+      <c r="AB1">
         <v>2047</v>
       </c>
-      <c r="Z1">
+      <c r="AC1">
         <v>2048</v>
       </c>
-      <c r="AA1">
+      <c r="AD1">
         <v>2049</v>
       </c>
-      <c r="AB1">
+      <c r="AE1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -2007,8 +2016,17 @@
       <c r="AB2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
@@ -2093,8 +2111,17 @@
       <c r="AB3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
@@ -2179,8 +2206,17 @@
       <c r="AB4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -2265,8 +2301,17 @@
       <c r="AB5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -2351,234 +2396,267 @@
       <c r="AB6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="5">
+        <f>'Global Renewables Outlook'!D7*(1-Wind!C4)</f>
+        <v>775076.77210135513</v>
+      </c>
+      <c r="C7" s="5">
+        <f>'Global Renewables Outlook'!E7*(1-Wind!D4)</f>
+        <v>900121.1891292074</v>
+      </c>
+      <c r="D7" s="5">
+        <f>'Global Renewables Outlook'!F7*(1-Wind!E4)</f>
+        <v>1022725.7338070514</v>
+      </c>
+      <c r="E7" s="5">
         <f>'Global Renewables Outlook'!G7*(1-Wind!F4)</f>
         <v>1136893.5130293544</v>
       </c>
-      <c r="C7" s="5">
+      <c r="F7" s="5">
         <f>'Global Renewables Outlook'!H7*(1-Wind!G4)</f>
         <v>1250773.9377340297</v>
       </c>
-      <c r="D7" s="5">
+      <c r="G7" s="5">
         <f>'Global Renewables Outlook'!I7*(1-Wind!H4)</f>
         <v>1362489.7806542467</v>
       </c>
-      <c r="E7" s="5">
+      <c r="H7" s="5">
         <f>'Global Renewables Outlook'!J7*(1-Wind!I4)</f>
         <v>1478640.9639649629</v>
       </c>
-      <c r="F7" s="5">
+      <c r="I7" s="5">
         <f>'Global Renewables Outlook'!K7*(1-Wind!J4)</f>
         <v>1597697.3311929598</v>
       </c>
-      <c r="G7" s="5">
+      <c r="J7" s="5">
         <f>'Global Renewables Outlook'!L7*(1-Wind!K4)</f>
         <v>1711604.7180015468</v>
       </c>
-      <c r="H7" s="5">
+      <c r="K7" s="5">
         <f>'Global Renewables Outlook'!M7*(1-Wind!L4)</f>
         <v>1819392.3548773606</v>
       </c>
-      <c r="I7" s="5">
+      <c r="L7" s="5">
         <f>'Global Renewables Outlook'!N7*(1-Wind!M4)</f>
         <v>1875002.5415982381</v>
       </c>
-      <c r="J7" s="5">
+      <c r="M7" s="5">
         <f>'Global Renewables Outlook'!O7*(1-Wind!N4)</f>
         <v>1927756.7115537715</v>
       </c>
-      <c r="K7" s="5">
+      <c r="N7" s="5">
         <f>'Global Renewables Outlook'!P7*(1-Wind!O4)</f>
         <v>1987962.964126393</v>
       </c>
-      <c r="L7" s="5">
+      <c r="O7" s="5">
         <f>'Global Renewables Outlook'!Q7*(1-Wind!P4)</f>
         <v>2048972.6988752473</v>
       </c>
-      <c r="M7" s="5">
+      <c r="P7" s="5">
         <f>'Global Renewables Outlook'!R7*(1-Wind!Q4)</f>
         <v>2129959.9682737119</v>
       </c>
-      <c r="N7" s="5">
+      <c r="Q7" s="5">
         <f>'Global Renewables Outlook'!S7*(1-Wind!R4)</f>
         <v>2215932.3022829583</v>
       </c>
-      <c r="O7" s="5">
+      <c r="R7" s="5">
         <f>'Global Renewables Outlook'!T7*(1-Wind!S4)</f>
         <v>2299960.4441534309</v>
       </c>
-      <c r="P7" s="5">
+      <c r="S7" s="5">
         <f>'Global Renewables Outlook'!U7*(1-Wind!T4)</f>
         <v>2383142.2667729277</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="T7" s="5">
         <f>'Global Renewables Outlook'!V7*(1-Wind!U4)</f>
         <v>2468216.8235020074</v>
       </c>
-      <c r="R7" s="5">
+      <c r="U7" s="5">
         <f>'Global Renewables Outlook'!W7*(1-Wind!V4)</f>
         <v>2550880.1051850733</v>
       </c>
-      <c r="S7" s="5">
+      <c r="V7" s="5">
         <f>'Global Renewables Outlook'!X7*(1-Wind!W4)</f>
         <v>2634875.7242717026</v>
       </c>
-      <c r="T7" s="5">
+      <c r="W7" s="5">
         <f>'Global Renewables Outlook'!Y7*(1-Wind!X4)</f>
         <v>2719858.0306125535</v>
       </c>
-      <c r="U7" s="5">
+      <c r="X7" s="5">
         <f>'Global Renewables Outlook'!Z7*(1-Wind!Y4)</f>
         <v>2805844.6273935628</v>
       </c>
-      <c r="V7" s="5">
+      <c r="Y7" s="5">
         <f>'Global Renewables Outlook'!AA7*(1-Wind!Z4)</f>
         <v>2890101.1357675246</v>
       </c>
-      <c r="W7" s="5">
+      <c r="Z7" s="5">
         <f>'Global Renewables Outlook'!AB7*(1-Wind!AA4)</f>
         <v>2972372.4111485863</v>
       </c>
-      <c r="X7" s="5">
+      <c r="AA7" s="5">
         <f>'Global Renewables Outlook'!AC7*(1-Wind!AB4)</f>
         <v>3062242.8847385035</v>
       </c>
-      <c r="Y7" s="5">
+      <c r="AB7" s="5">
         <f>'Global Renewables Outlook'!AD7*(1-Wind!AC4)</f>
         <v>3154247.9605017747</v>
       </c>
-      <c r="Z7" s="5">
+      <c r="AC7" s="5">
         <f>'Global Renewables Outlook'!AE7*(1-Wind!AD4)</f>
         <v>3241643.3280328619</v>
       </c>
-      <c r="AA7" s="5">
+      <c r="AD7" s="5">
         <f>'Global Renewables Outlook'!AF7*(1-Wind!AE4)</f>
         <v>3329824.154709897</v>
       </c>
-      <c r="AB7" s="5">
+      <c r="AE7" s="5">
         <f>'Global Renewables Outlook'!AG7*(1-Wind!AF4)</f>
         <v>3423108.1235600994</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="5">
+        <f>'Global Renewables Outlook'!D6</f>
+        <v>924779.99999991152</v>
+      </c>
+      <c r="C8" s="5">
+        <f>'Global Renewables Outlook'!E6</f>
+        <v>1344133.3333333023</v>
+      </c>
+      <c r="D8" s="5">
+        <f>'Global Renewables Outlook'!F6</f>
+        <v>1763486.6666665766</v>
+      </c>
+      <c r="E8" s="5">
         <f>'Global Renewables Outlook'!G6</f>
         <v>2182839.9999999674</v>
       </c>
-      <c r="C8" s="5">
+      <c r="F8" s="5">
         <f>'Global Renewables Outlook'!H6</f>
         <v>2602193.3333332418</v>
       </c>
-      <c r="D8" s="5">
+      <c r="G8" s="5">
         <f>'Global Renewables Outlook'!I6</f>
         <v>3021546.6666666325</v>
       </c>
-      <c r="E8" s="5">
+      <c r="H8" s="5">
         <f>'Global Renewables Outlook'!J6</f>
         <v>3440899.9999999069</v>
       </c>
-      <c r="F8" s="5">
+      <c r="I8" s="5">
         <f>'Global Renewables Outlook'!K6</f>
         <v>3860253.3333332976</v>
       </c>
-      <c r="G8" s="5">
+      <c r="J8" s="5">
         <f>'Global Renewables Outlook'!L6</f>
         <v>4279606.666666572</v>
       </c>
-      <c r="H8" s="5">
+      <c r="K8" s="5">
         <f>'Global Renewables Outlook'!M6</f>
         <v>4698959.9999999627</v>
       </c>
-      <c r="I8" s="5">
+      <c r="L8" s="5">
         <f>'Global Renewables Outlook'!N6</f>
         <v>5095961.9999999413</v>
       </c>
-      <c r="J8" s="5">
+      <c r="M8" s="5">
         <f>'Global Renewables Outlook'!O6</f>
         <v>5492963.9999999199</v>
       </c>
-      <c r="K8" s="5">
+      <c r="N8" s="5">
         <f>'Global Renewables Outlook'!P6</f>
         <v>5889965.9999998985</v>
       </c>
-      <c r="L8" s="5">
+      <c r="O8" s="5">
         <f>'Global Renewables Outlook'!Q6</f>
         <v>6286967.9999998771</v>
       </c>
-      <c r="M8" s="5">
+      <c r="P8" s="5">
         <f>'Global Renewables Outlook'!R6</f>
         <v>6683969.9999999721</v>
       </c>
-      <c r="N8" s="5">
+      <c r="Q8" s="5">
         <f>'Global Renewables Outlook'!S6</f>
         <v>7080971.9999999506</v>
       </c>
-      <c r="O8" s="5">
+      <c r="R8" s="5">
         <f>'Global Renewables Outlook'!T6</f>
         <v>7477973.9999999292</v>
       </c>
-      <c r="P8" s="5">
+      <c r="S8" s="5">
         <f>'Global Renewables Outlook'!U6</f>
         <v>7874975.9999999078</v>
       </c>
-      <c r="Q8" s="5">
+      <c r="T8" s="5">
         <f>'Global Renewables Outlook'!V6</f>
         <v>8271977.9999998864</v>
       </c>
-      <c r="R8" s="5">
+      <c r="U8" s="5">
         <f>'Global Renewables Outlook'!W6</f>
         <v>8668979.9999999814</v>
       </c>
-      <c r="S8" s="5">
+      <c r="V8" s="5">
         <f>'Global Renewables Outlook'!X6</f>
         <v>9065981.999999959</v>
       </c>
-      <c r="T8" s="5">
+      <c r="W8" s="5">
         <f>'Global Renewables Outlook'!Y6</f>
         <v>9462983.9999999385</v>
       </c>
-      <c r="U8" s="5">
+      <c r="X8" s="5">
         <f>'Global Renewables Outlook'!Z6</f>
         <v>9859985.999999918</v>
       </c>
-      <c r="V8" s="5">
+      <c r="Y8" s="5">
         <f>'Global Renewables Outlook'!AA6</f>
         <v>10256987.999999896</v>
       </c>
-      <c r="W8" s="5">
+      <c r="Z8" s="5">
         <f>'Global Renewables Outlook'!AB6</f>
         <v>10653989.999999873</v>
       </c>
-      <c r="X8" s="5">
+      <c r="AA8" s="5">
         <f>'Global Renewables Outlook'!AC6</f>
         <v>11050991.99999997</v>
       </c>
-      <c r="Y8" s="5">
+      <c r="AB8" s="5">
         <f>'Global Renewables Outlook'!AD6</f>
         <v>11447993.999999948</v>
       </c>
-      <c r="Z8" s="5">
+      <c r="AC8" s="5">
         <f>'Global Renewables Outlook'!AE6</f>
         <v>11844995.999999925</v>
       </c>
-      <c r="AA8" s="5">
+      <c r="AD8" s="5">
         <f>'Global Renewables Outlook'!AF6</f>
         <v>12241997.999999905</v>
       </c>
-      <c r="AB8" s="5">
+      <c r="AE8" s="5">
         <f>'Global Renewables Outlook'!AG6</f>
         <v>12638999.999999885</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2663,8 +2741,17 @@
       <c r="AB9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -2749,8 +2836,17 @@
       <c r="AB10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -2835,8 +2931,17 @@
       <c r="AB11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
@@ -2921,8 +3026,17 @@
       <c r="AB12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
@@ -3007,8 +3121,17 @@
       <c r="AB13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
@@ -3093,121 +3216,142 @@
       <c r="AB14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="5">
+        <f>'Global Renewables Outlook'!D7*Wind!B4</f>
+        <v>40088.585855819823</v>
+      </c>
+      <c r="C15" s="5">
+        <f>'Global Renewables Outlook'!E7*Wind!C4</f>
+        <v>60552.682810726183</v>
+      </c>
+      <c r="D15" s="5">
+        <f>'Global Renewables Outlook'!F7*Wind!D4</f>
+        <v>73490.060248979091</v>
+      </c>
+      <c r="E15" s="5">
         <f>'Global Renewables Outlook'!G7*Wind!E4</f>
         <v>89037.595218580886</v>
       </c>
-      <c r="C15" s="5">
+      <c r="F15" s="5">
         <f>'Global Renewables Outlook'!H7*Wind!F4</f>
         <v>113800.59291611612</v>
       </c>
-      <c r="D15" s="5">
+      <c r="G15" s="5">
         <f>'Global Renewables Outlook'!I7*Wind!G4</f>
         <v>138582.86918859708</v>
       </c>
-      <c r="E15" s="5">
+      <c r="H15" s="5">
         <f>'Global Renewables Outlook'!J7*Wind!H4</f>
         <v>165505.04431378981</v>
       </c>
-      <c r="F15" s="5">
+      <c r="I15" s="5">
         <f>'Global Renewables Outlook'!K7*Wind!I4</f>
         <v>187424.14160128735</v>
       </c>
-      <c r="G15" s="5">
+      <c r="J15" s="5">
         <f>'Global Renewables Outlook'!L7*Wind!J4</f>
         <v>206118.71382443423</v>
       </c>
-      <c r="H15" s="5">
+      <c r="K15" s="5">
         <f>'Global Renewables Outlook'!M7*Wind!K4</f>
         <v>230285.87337236118</v>
       </c>
-      <c r="I15" s="5">
+      <c r="L15" s="5">
         <f>'Global Renewables Outlook'!N7*Wind!L4</f>
         <v>255332.93188794897</v>
       </c>
-      <c r="J15" s="5">
+      <c r="M15" s="5">
         <f>'Global Renewables Outlook'!O7*Wind!M4</f>
         <v>291237.77865488769</v>
       </c>
-      <c r="K15" s="5">
+      <c r="N15" s="5">
         <f>'Global Renewables Outlook'!P7*Wind!N4</f>
         <v>330031.93771321455</v>
       </c>
-      <c r="L15" s="5">
+      <c r="O15" s="5">
         <f>'Global Renewables Outlook'!Q7*Wind!O4</f>
         <v>361004.00300979265</v>
       </c>
-      <c r="M15" s="5">
+      <c r="P15" s="5">
         <f>'Global Renewables Outlook'!R7*Wind!P4</f>
         <v>391092.00464981049</v>
       </c>
-      <c r="N15" s="5">
+      <c r="Q15" s="5">
         <f>'Global Renewables Outlook'!S7*Wind!Q4</f>
         <v>400441.03425807011</v>
       </c>
-      <c r="O15" s="5">
+      <c r="R15" s="5">
         <f>'Global Renewables Outlook'!T7*Wind!R4</f>
         <v>404643.31207967794</v>
       </c>
-      <c r="P15" s="5">
+      <c r="S15" s="5">
         <f>'Global Renewables Outlook'!U7*Wind!S4</f>
         <v>410876.84215022629</v>
       </c>
-      <c r="Q15" s="5">
+      <c r="T15" s="5">
         <f>'Global Renewables Outlook'!V7*Wind!T4</f>
         <v>417999.63597350329</v>
       </c>
-      <c r="R15" s="5">
+      <c r="U15" s="5">
         <f>'Global Renewables Outlook'!W7*Wind!U4</f>
         <v>423182.47386574256</v>
       </c>
-      <c r="S15" s="5">
+      <c r="V15" s="5">
         <f>'Global Renewables Outlook'!X7*Wind!V4</f>
         <v>430864.87645209447</v>
       </c>
-      <c r="T15" s="5">
+      <c r="W15" s="5">
         <f>'Global Renewables Outlook'!Y7*Wind!W4</f>
         <v>437184.66041645262</v>
       </c>
-      <c r="U15" s="5">
+      <c r="X15" s="5">
         <f>'Global Renewables Outlook'!Z7*Wind!X4</f>
         <v>442500.01644445065</v>
       </c>
-      <c r="V15" s="5">
+      <c r="Y15" s="5">
         <f>'Global Renewables Outlook'!AA7*Wind!Y4</f>
         <v>446794.33610616927</v>
       </c>
-      <c r="W15" s="5">
+      <c r="Z15" s="5">
         <f>'Global Renewables Outlook'!AB7*Wind!Z4</f>
         <v>452877.65354890848</v>
       </c>
-      <c r="X15" s="5">
+      <c r="AA15" s="5">
         <f>'Global Renewables Outlook'!AC7*Wind!AA4</f>
         <v>461007.18750435935</v>
       </c>
-      <c r="Y15" s="5">
+      <c r="AB15" s="5">
         <f>'Global Renewables Outlook'!AD7*Wind!AB4</f>
         <v>461346.81313483516</v>
       </c>
-      <c r="Z15" s="5">
+      <c r="AC15" s="5">
         <f>'Global Renewables Outlook'!AE7*Wind!AC4</f>
         <v>459512.7777562656</v>
       </c>
-      <c r="AA15" s="5">
+      <c r="AD15" s="5">
         <f>'Global Renewables Outlook'!AF7*Wind!AD4</f>
         <v>462417.53814992314</v>
       </c>
-      <c r="AB15" s="5">
+      <c r="AE15" s="5">
         <f>'Global Renewables Outlook'!AG7*Wind!AE4</f>
         <v>464527.61322951212</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
@@ -3292,8 +3436,17 @@
       <c r="AB16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -3378,8 +3531,17 @@
       <c r="AB17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
@@ -3464,8 +3626,17 @@
       <c r="AB18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -3550,8 +3721,17 @@
       <c r="AB19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -3636,8 +3816,17 @@
       <c r="AB20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -3722,8 +3911,17 @@
       <c r="AB21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -3808,8 +4006,17 @@
       <c r="AB22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -3894,8 +4101,17 @@
       <c r="AB23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>35</v>
       </c>
@@ -3980,8 +4196,17 @@
       <c r="AB24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>36</v>
       </c>
@@ -4064,6 +4289,15 @@
         <v>0</v>
       </c>
       <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
         <v>0</v>
       </c>
     </row>
